--- a/data/b2_indio/B2 Índio 10-2025.xlsx
+++ b/data/b2_indio/B2 Índio 10-2025.xlsx
@@ -4824,20 +4824,20 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>45935</v>
+        <v>45932</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>52360.67</v>
+        <v>3345.26</v>
       </c>
     </row>
     <row r="3">
@@ -4846,34 +4846,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>2147.33</v>
+        <v>52604.12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>45936</v>
+        <v>45935</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>1430.78</v>
+        <v>2274.43</v>
       </c>
     </row>
     <row r="5">
@@ -4887,11 +4887,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>926.55</v>
+        <v>1608.18</v>
       </c>
     </row>
     <row r="6">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>2871.94</v>
+        <v>2916.56</v>
       </c>
     </row>
     <row r="8">
@@ -4945,79 +4945,79 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1993.59</v>
+        <v>1958.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1383.25</v>
+        <v>9379.91</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>3595.95</v>
+        <v>1476.07</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>45945</v>
+        <v>45948</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>9744.969999999999</v>
+        <v>1424.71</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>45945</v>
+        <v>45949</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1328.11</v>
+        <v>1045.96</v>
       </c>
     </row>
     <row r="13">
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>3174.69</v>
+        <v>3155.51</v>
       </c>
     </row>
     <row r="14">
@@ -5053,25 +5053,25 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>18298.24</v>
+        <v>18415.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>45956</v>
+        <v>45954</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>1060.19</v>
+        <v>1702.41</v>
       </c>
     </row>
     <row r="16">
@@ -5089,7 +5089,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3266.48</v>
+        <v>2969.46</v>
       </c>
     </row>
     <row r="17">
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>2291.92</v>
+        <v>2293.74</v>
       </c>
     </row>
   </sheetData>
